--- a/Phenotype/Tables/EPS_TableS8A_FromR.xlsx
+++ b/Phenotype/Tables/EPS_TableS8A_FromR.xlsx
@@ -377,7 +377,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Pr(&gt;F)</t>
         </is>
       </c>
     </row>
